--- a/tcc-documentacao/Planejamento/Requisitos/requisitos-denuncias-urbanas.xlsx
+++ b/tcc-documentacao/Planejamento/Requisitos/requisitos-denuncias-urbanas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\Requisitos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\Requisitos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64AA80FA-8589-448C-93F8-BE56866F7552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1748F659-4C22-453A-81E0-C1BF87B7DB29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{352A2108-1EAB-4B7E-8DF7-D5280156B846}"/>
   </bookViews>
@@ -18,28 +18,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$C$2</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="110">
   <si>
     <t>Requisitos Funcionais Site (Usuário e administrador)</t>
   </si>
@@ -309,13 +298,73 @@
   </si>
   <si>
     <t>Órgão/Empresa — O sistema deve permitir que o órgão público ou empresa atualize as informações de seu perfil institucional, conforme as permissões definidas pelo administrador.</t>
+  </si>
+  <si>
+    <t>Codigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requisitos não-funcionais SITE </t>
+  </si>
+  <si>
+    <t>O site deve apresentar responsividade se ajustando a qualquer tipo e tamanho de tela.</t>
+  </si>
+  <si>
+    <t>O site deve apresentar desempenho rápido, com suas páginas carregando em até 3 segundos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> O site deve apresentar usabilidade com navegação simples e intuitiva.</t>
+  </si>
+  <si>
+    <t>O sistema deve priorizar a privacidade, protegendo os dados do usuário.</t>
+  </si>
+  <si>
+    <t>O site deve estar disponivel 24h por dia.</t>
+  </si>
+  <si>
+    <t>O site deve ser protegido e seguro contra invasores mal intencionados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O site deve ter escalabilidade, suportando o aumento do número de usuários sem perder seu desempenho.   </t>
+  </si>
+  <si>
+    <t>O site deve ser de fácil manutenção e organizado para futuras alterações.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requisitos não Funcionais APP </t>
+  </si>
+  <si>
+    <t>O aplicativo deve apresentar um desmpenho rápido ao responder os comandos do usuário.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve ser otimizado para rodar em dispositivos mais fracos.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve conter funções fáceis de encontrar e  utilizar.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve ser estável, evitando falhas inesperadas durante o uso.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve ser escalavel, conseguindo atender grandes quantidades de usuários.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve priorizar a privacidade, protegendo os dados dos usuários.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve ser seguro contra invasores mal intencionados e malwares.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve ser capaz de realizar backups  recuperação após trocas de disposivo ou falhas.</t>
+  </si>
+  <si>
+    <t>O aplicativo deve incializar de maneira ligeira em poucos segundos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,8 +399,39 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="mes New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="mes New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,6 +447,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -529,6 +615,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -549,7 +653,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -845,18 +949,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824C14D4-FCA1-45E7-9429-E52589449756}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="46.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="7" max="7" width="36.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="46.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="6" max="6" width="16.54296875" customWidth="1"/>
+    <col min="7" max="7" width="36.26953125" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" customWidth="1"/>
+    <col min="12" max="12" width="28.08984375" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" customWidth="1"/>
+    <col min="16" max="16" width="15.81640625" customWidth="1"/>
+    <col min="17" max="17" width="30.08984375" customWidth="1"/>
+    <col min="18" max="18" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.45" customHeight="1">
+    <row r="1" spans="1:18" ht="14.5" customHeight="1">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -867,8 +977,18 @@
       </c>
       <c r="G1" s="21"/>
       <c r="H1" s="22"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75">
+      <c r="K1" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="P1" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="22"/>
+    </row>
+    <row r="2" spans="1:18" ht="30">
       <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
@@ -887,8 +1007,26 @@
       <c r="H2" s="16" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="61.5">
+      <c r="K2" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="80" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>5</v>
       </c>
@@ -907,8 +1045,26 @@
       <c r="H3" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="61.5">
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="62">
       <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
@@ -927,8 +1083,26 @@
       <c r="H4" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="61.5">
+      <c r="K4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="62">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
@@ -947,8 +1121,26 @@
       <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="45.75">
+      <c r="K5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="46.5">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
@@ -967,8 +1159,26 @@
       <c r="H6" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="61.5">
+      <c r="K6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="62">
       <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
@@ -987,8 +1197,26 @@
       <c r="H7" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="76.5">
+      <c r="K7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="62">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -1007,8 +1235,26 @@
       <c r="H8" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="76.5">
+      <c r="K8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="77.5">
       <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
@@ -1027,8 +1273,26 @@
       <c r="H9" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="61.5">
+      <c r="K9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="62">
       <c r="A10" s="8" t="s">
         <v>29</v>
       </c>
@@ -1047,8 +1311,26 @@
       <c r="H10" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="76.5">
+      <c r="K10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="77.5">
       <c r="A11" s="8" t="s">
         <v>32</v>
       </c>
@@ -1067,8 +1349,26 @@
       <c r="H11" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="76.5">
+      <c r="K11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="77.5">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -1088,7 +1388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="45.75">
+    <row r="13" spans="1:18" ht="46.5">
       <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
@@ -1108,7 +1408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="61.5">
+    <row r="14" spans="1:18" ht="62">
       <c r="A14" s="8" t="s">
         <v>41</v>
       </c>
@@ -1128,7 +1428,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="61.5">
+    <row r="15" spans="1:18" ht="62">
       <c r="A15" s="8" t="s">
         <v>44</v>
       </c>
@@ -1148,7 +1448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="91.5">
+    <row r="16" spans="1:18" ht="77.5">
       <c r="A16" s="8" t="s">
         <v>47</v>
       </c>
@@ -1168,7 +1468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="61.5">
+    <row r="17" spans="1:8" ht="46.5">
       <c r="A17" s="8" t="s">
         <v>50</v>
       </c>
@@ -1188,7 +1488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="45.75">
+    <row r="18" spans="1:8" ht="46.5">
       <c r="A18" s="8" t="s">
         <v>52</v>
       </c>
@@ -1202,7 +1502,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="45.75">
+    <row r="19" spans="1:8" ht="46.5">
       <c r="A19" s="8" t="s">
         <v>54</v>
       </c>
@@ -1222,7 +1522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="45.75">
+    <row r="20" spans="1:8" ht="31">
       <c r="A20" s="8" t="s">
         <v>57</v>
       </c>
@@ -1242,7 +1542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="45.75">
+    <row r="21" spans="1:8" ht="46.5">
       <c r="A21" s="8" t="s">
         <v>59</v>
       </c>
@@ -1262,7 +1562,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="61.5">
+    <row r="22" spans="1:8" ht="62">
       <c r="A22" s="8" t="s">
         <v>62</v>
       </c>
@@ -1282,7 +1582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="45.75">
+    <row r="23" spans="1:8" ht="46.5">
       <c r="A23" s="8" t="s">
         <v>64</v>
       </c>
@@ -1302,7 +1602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="61.5">
+    <row r="24" spans="1:8" ht="62">
       <c r="A24" s="8" t="s">
         <v>67</v>
       </c>
@@ -1322,7 +1622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="91.5">
+    <row r="25" spans="1:8" ht="77.5">
       <c r="A25" s="8" t="s">
         <v>71</v>
       </c>
@@ -1342,7 +1642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="84.95" customHeight="1">
+    <row r="26" spans="1:8" ht="85" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>74</v>
       </c>
@@ -1353,7 +1653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="84.95" customHeight="1">
+    <row r="27" spans="1:8" ht="85" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>76</v>
       </c>
@@ -1364,7 +1664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="76.5">
+    <row r="28" spans="1:8" ht="77.5">
       <c r="A28" s="8" t="s">
         <v>78</v>
       </c>
@@ -1375,7 +1675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="61.5">
+    <row r="29" spans="1:8" ht="62">
       <c r="A29" s="8" t="s">
         <v>80</v>
       </c>
@@ -1386,7 +1686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="61.5">
+    <row r="30" spans="1:8" ht="62">
       <c r="A30" s="8" t="s">
         <v>82</v>
       </c>
@@ -1397,7 +1697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="61.5">
+    <row r="31" spans="1:8" ht="62">
       <c r="A31" s="8" t="s">
         <v>84</v>
       </c>
@@ -1408,7 +1708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="61.5">
+    <row r="32" spans="1:8" ht="62">
       <c r="A32" s="8" t="s">
         <v>86</v>
       </c>
@@ -1419,7 +1719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="76.5">
+    <row r="33" spans="1:3" ht="77.5">
       <c r="A33" s="8" t="s">
         <v>88</v>
       </c>
@@ -1437,9 +1737,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:C27" xr:uid="{824C14D4-FCA1-45E7-9429-E52589449756}"/>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="P1:R1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
